--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -2960,7 +2960,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134039377</v>
+        <v>134039376</v>
       </c>
       <c r="B23" t="n">
         <v>96769</v>
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575819</v>
+        <v>575675</v>
       </c>
       <c r="R23" t="n">
-        <v>6338837</v>
+        <v>6338821</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134039376</v>
+        <v>134039377</v>
       </c>
       <c r="B24" t="n">
         <v>96769</v>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575675</v>
+        <v>575819</v>
       </c>
       <c r="R24" t="n">
-        <v>6338821</v>
+        <v>6338837</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3154,10 +3154,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134039379</v>
+        <v>134039372</v>
       </c>
       <c r="B25" t="n">
-        <v>96769</v>
+        <v>97457</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,21 +3165,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>2590</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575755</v>
+        <v>575722</v>
       </c>
       <c r="R25" t="n">
-        <v>6338857</v>
+        <v>6338748</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134039372</v>
+        <v>134039379</v>
       </c>
       <c r="B26" t="n">
-        <v>97457</v>
+        <v>96769</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,21 +3262,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575722</v>
+        <v>575755</v>
       </c>
       <c r="R26" t="n">
-        <v>6338748</v>
+        <v>6338857</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -2362,7 +2362,7 @@
         <v>134039367</v>
       </c>
       <c r="B17" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>134039380</v>
       </c>
       <c r="B19" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>134039378</v>
       </c>
       <c r="B21" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134039376</v>
+        <v>134039377</v>
       </c>
       <c r="B23" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575675</v>
+        <v>575819</v>
       </c>
       <c r="R23" t="n">
-        <v>6338821</v>
+        <v>6338837</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3057,10 +3057,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134039377</v>
+        <v>134039376</v>
       </c>
       <c r="B24" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575819</v>
+        <v>575675</v>
       </c>
       <c r="R24" t="n">
-        <v>6338837</v>
+        <v>6338821</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3154,10 +3154,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134039372</v>
+        <v>134039379</v>
       </c>
       <c r="B25" t="n">
-        <v>97457</v>
+        <v>96776</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,21 +3165,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575722</v>
+        <v>575755</v>
       </c>
       <c r="R25" t="n">
-        <v>6338748</v>
+        <v>6338857</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134039379</v>
+        <v>134039372</v>
       </c>
       <c r="B26" t="n">
-        <v>96769</v>
+        <v>97464</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,21 +3262,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>2590</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575755</v>
+        <v>575722</v>
       </c>
       <c r="R26" t="n">
-        <v>6338857</v>
+        <v>6338748</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3351,7 +3351,7 @@
         <v>134039371</v>
       </c>
       <c r="B27" t="n">
-        <v>97457</v>
+        <v>97464</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114872789</v>
+        <v>114872731</v>
       </c>
       <c r="B2" t="n">
-        <v>95242</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575667</v>
+        <v>575686</v>
       </c>
       <c r="R2" t="n">
-        <v>6338849</v>
+        <v>6338891</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -782,54 +777,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114872751</v>
+        <v>115173056</v>
       </c>
       <c r="B3" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575659</v>
+        <v>575620</v>
       </c>
       <c r="R3" t="n">
-        <v>6338885</v>
+        <v>6338869</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -856,12 +845,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,55 +876,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114872769</v>
+        <v>134039367</v>
       </c>
       <c r="B4" t="n">
-        <v>95242</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575684</v>
+        <v>575730</v>
       </c>
       <c r="R4" t="n">
-        <v>6338893</v>
+        <v>6338781</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -963,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,15 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114872727</v>
+        <v>114872798</v>
       </c>
       <c r="B5" t="n">
-        <v>95242</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575686</v>
+        <v>575684</v>
       </c>
       <c r="R5" t="n">
-        <v>6338891</v>
+        <v>6338822</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1103,54 +1091,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114872731</v>
+        <v>134039376</v>
       </c>
       <c r="B6" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575686</v>
+        <v>575675</v>
       </c>
       <c r="R6" t="n">
-        <v>6338891</v>
+        <v>6338821</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1177,12 +1156,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,7 +1170,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1210,15 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114872798</v>
+        <v>134039377</v>
       </c>
       <c r="B7" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1244,20 +1217,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575684</v>
+        <v>575819</v>
       </c>
       <c r="R7" t="n">
-        <v>6338822</v>
+        <v>6338837</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1284,12 +1253,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1298,7 +1267,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1317,15 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114872719</v>
+        <v>134039378</v>
       </c>
       <c r="B8" t="n">
-        <v>95242</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,38 +1296,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575678</v>
+        <v>575798</v>
       </c>
       <c r="R8" t="n">
-        <v>6338931</v>
+        <v>6338862</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1391,12 +1350,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,7 +1364,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1424,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115173209</v>
+        <v>134039379</v>
       </c>
       <c r="B9" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,46 +1393,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575688</v>
+        <v>575755</v>
       </c>
       <c r="R9" t="n">
-        <v>6338871</v>
+        <v>6338857</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1506,22 +1447,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,27 +1467,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115173297</v>
+        <v>134039380</v>
       </c>
       <c r="B10" t="n">
-        <v>95242</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,38 +1490,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575651</v>
+        <v>575719</v>
       </c>
       <c r="R10" t="n">
-        <v>6338902</v>
+        <v>6338853</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1622,22 +1544,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,34 +1558,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115173284</v>
+        <v>115434703</v>
       </c>
       <c r="B11" t="n">
-        <v>95242</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,38 +1587,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575680</v>
+        <v>575686</v>
       </c>
       <c r="R11" t="n">
-        <v>6338897</v>
+        <v>6338891</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1739,22 +1641,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,34 +1655,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115173183</v>
+        <v>115474054</v>
       </c>
       <c r="B12" t="n">
-        <v>95242</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,21 +1684,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2590</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1826,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575688</v>
+        <v>575680</v>
       </c>
       <c r="R12" t="n">
-        <v>6338871</v>
+        <v>6338885</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1856,22 +1742,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,15 +1785,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115434703</v>
+        <v>114872706</v>
       </c>
       <c r="B13" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,34 +1796,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>2590</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575686</v>
+        <v>575651</v>
       </c>
       <c r="R13" t="n">
-        <v>6338891</v>
+        <v>6338972</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1969,12 +1854,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,6 +1868,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2001,62 +1887,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115473966</v>
+        <v>114872719</v>
       </c>
       <c r="B14" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575648</v>
+        <v>575678</v>
       </c>
       <c r="R14" t="n">
-        <v>6338867</v>
+        <v>6338931</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2083,22 +1956,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,33 +1970,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115474054</v>
+        <v>114872727</v>
       </c>
       <c r="B15" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,21 +2000,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,14 +2024,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575680</v>
+        <v>575686</v>
       </c>
       <c r="R15" t="n">
-        <v>6338885</v>
+        <v>6338891</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2199,22 +2058,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,27 +2079,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115473932</v>
+        <v>114872769</v>
       </c>
       <c r="B16" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,21 +2102,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>2590</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2282,14 +2126,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575648</v>
+        <v>575684</v>
       </c>
       <c r="R16" t="n">
-        <v>6338867</v>
+        <v>6338893</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2316,22 +2160,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2347,49 +2181,50 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134039367</v>
+        <v>114872789</v>
       </c>
       <c r="B17" t="n">
-        <v>91967</v>
+        <v>97394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>2590</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2397,10 +2232,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575730</v>
+        <v>575667</v>
       </c>
       <c r="R17" t="n">
-        <v>6338781</v>
+        <v>6338849</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2427,12 +2262,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2460,10 +2295,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134039363</v>
+        <v>115173183</v>
       </c>
       <c r="B18" t="n">
-        <v>5201</v>
+        <v>97394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,34 +2306,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575729</v>
+        <v>575688</v>
       </c>
       <c r="R18" t="n">
-        <v>6338794</v>
+        <v>6338871</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2525,17 +2364,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2544,28 +2388,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134039380</v>
+        <v>115173284</v>
       </c>
       <c r="B19" t="n">
-        <v>96776</v>
+        <v>97394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,34 +2418,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>2590</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575719</v>
+        <v>575680</v>
       </c>
       <c r="R19" t="n">
-        <v>6338853</v>
+        <v>6338897</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2627,12 +2476,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2641,28 +2500,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134039374</v>
+        <v>115173297</v>
       </c>
       <c r="B20" t="n">
-        <v>5181</v>
+        <v>97394</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2670,34 +2530,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575729</v>
+        <v>575651</v>
       </c>
       <c r="R20" t="n">
-        <v>6338794</v>
+        <v>6338902</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2724,17 +2588,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2743,28 +2612,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134039378</v>
+        <v>134039371</v>
       </c>
       <c r="B21" t="n">
-        <v>96776</v>
+        <v>97471</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2772,21 +2642,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>2590</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2796,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575798</v>
+        <v>575685</v>
       </c>
       <c r="R21" t="n">
-        <v>6338862</v>
+        <v>6338794</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2858,32 +2728,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134039368</v>
+        <v>134039372</v>
       </c>
       <c r="B22" t="n">
-        <v>57972</v>
+        <v>97471</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2893,10 +2763,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575711</v>
+        <v>575722</v>
       </c>
       <c r="R22" t="n">
-        <v>6338746</v>
+        <v>6338748</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2929,11 +2799,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Födosöksspår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2960,10 +2825,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134039377</v>
+        <v>114872751</v>
       </c>
       <c r="B23" t="n">
-        <v>96776</v>
+        <v>96348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2971,34 +2836,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575819</v>
+        <v>575659</v>
       </c>
       <c r="R23" t="n">
-        <v>6338837</v>
+        <v>6338885</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3025,12 +2894,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3039,6 +2908,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3057,10 +2927,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134039376</v>
+        <v>123973813</v>
       </c>
       <c r="B24" t="n">
-        <v>96776</v>
+        <v>92333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3068,37 +2938,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>4217</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökklint, Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575675</v>
+        <v>575666</v>
       </c>
       <c r="R24" t="n">
-        <v>6338821</v>
+        <v>6338964</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3122,12 +2992,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,10 +3024,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134039379</v>
+        <v>134039364</v>
       </c>
       <c r="B25" t="n">
-        <v>96776</v>
+        <v>91937</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,21 +3035,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3189,10 +3059,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575755</v>
+        <v>575748</v>
       </c>
       <c r="R25" t="n">
-        <v>6338857</v>
+        <v>6338783</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3251,10 +3121,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134039372</v>
+        <v>123973504</v>
       </c>
       <c r="B26" t="n">
-        <v>97464</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,34 +3132,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575722</v>
+        <v>575611</v>
       </c>
       <c r="R26" t="n">
-        <v>6338748</v>
+        <v>6338932</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3316,12 +3191,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3348,10 +3223,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134039371</v>
+        <v>134039368</v>
       </c>
       <c r="B27" t="n">
-        <v>97464</v>
+        <v>57972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,21 +3234,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3383,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575685</v>
+        <v>575711</v>
       </c>
       <c r="R27" t="n">
-        <v>6338794</v>
+        <v>6338746</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3421,6 +3296,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Födosöksspår</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3442,6 +3322,679 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134039374</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>575729</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6338794</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>115173209</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>575688</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6338871</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>115173318</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>575598</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6338927</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>115473966</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>575648</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6338867</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134039363</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>575729</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6338794</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>115473932</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>575648</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6338867</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114872731</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115173056</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039367</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114872798</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039376</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039377</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039378</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039379</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039380</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1670,6 +1720,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115434703</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1782,6 +1837,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115474054</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114872706</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1986,6 +2051,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114872719</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2088,6 +2158,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114872727</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2190,6 +2265,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114872769</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2292,6 +2372,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114872789</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2404,6 +2489,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115173183</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2516,6 +2606,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115173284</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2628,6 +2723,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115173297</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2725,6 +2825,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039371</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2822,6 +2927,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039372</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2924,6 +3034,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114872751</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3021,6 +3136,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123973813</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3118,6 +3238,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039364</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3220,6 +3345,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123973504</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3322,6 +3452,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039368</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3424,6 +3559,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039374</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3543,6 +3683,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115173209</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3662,6 +3807,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115173318</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3781,6 +3931,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115473966</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3883,6 +4038,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039363</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3995,8 +4155,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115473932</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115173056</v>
+        <v>135819428</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>97511</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,40 +798,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökhult Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575620</v>
+        <v>575647</v>
       </c>
       <c r="R3" t="n">
-        <v>6338869</v>
+        <v>6338758</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,22 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,27 +877,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115173056</t>
+          <t>https://artportalen.se/Sighting/135819428</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134039367</v>
+        <v>135819786</v>
       </c>
       <c r="B4" t="n">
-        <v>91974</v>
+        <v>97511</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,40 +905,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökhult Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575730</v>
+        <v>575667</v>
       </c>
       <c r="R4" t="n">
-        <v>6338781</v>
+        <v>6338745</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,49 +984,49 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039367</t>
+          <t>https://artportalen.se/Sighting/135819786</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114872798</v>
+        <v>135819791</v>
       </c>
       <c r="B5" t="n">
-        <v>96708</v>
+        <v>97511</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,17 +1036,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökhult Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575684</v>
+        <v>575748</v>
       </c>
       <c r="R5" t="n">
-        <v>6338822</v>
+        <v>6338819</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,12 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,65 +1091,69 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114872798</t>
+          <t>https://artportalen.se/Sighting/135819791</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134039376</v>
+        <v>135819811</v>
       </c>
       <c r="B6" t="n">
-        <v>96783</v>
+        <v>97511</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökhult Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575675</v>
+        <v>575808</v>
       </c>
       <c r="R6" t="n">
-        <v>6338821</v>
+        <v>6338788</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,12 +1177,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,71 +1191,76 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039376</t>
+          <t>https://artportalen.se/Sighting/135819811</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134039377</v>
+        <v>135819813</v>
       </c>
       <c r="B7" t="n">
-        <v>96783</v>
+        <v>97511</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökhult Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575819</v>
+        <v>575685</v>
       </c>
       <c r="R7" t="n">
-        <v>6338837</v>
+        <v>6338721</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,12 +1284,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,33 +1298,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039377</t>
+          <t>https://artportalen.se/Sighting/135819813</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134039378</v>
+        <v>135819199</v>
       </c>
       <c r="B8" t="n">
-        <v>96783</v>
+        <v>96705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,37 +1333,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökhult Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575798</v>
+        <v>575826</v>
       </c>
       <c r="R8" t="n">
-        <v>6338862</v>
+        <v>6338771</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1385,12 +1391,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,68 +1405,72 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039378</t>
+          <t>https://artportalen.se/Sighting/135819199</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134039379</v>
+        <v>115173056</v>
       </c>
       <c r="B9" t="n">
-        <v>96783</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575755</v>
+        <v>575620</v>
       </c>
       <c r="R9" t="n">
-        <v>6338857</v>
+        <v>6338869</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1487,12 +1497,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,68 +1521,72 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039379</t>
+          <t>https://artportalen.se/Sighting/115173056</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134039380</v>
+        <v>134039367</v>
       </c>
       <c r="B10" t="n">
-        <v>96783</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575719</v>
+        <v>575730</v>
       </c>
       <c r="R10" t="n">
-        <v>6338853</v>
+        <v>6338781</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1603,6 +1627,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1620,54 +1645,57 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039380</t>
+          <t>https://artportalen.se/Sighting/134039367</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115434703</v>
+        <v>135819616</v>
       </c>
       <c r="B11" t="n">
-        <v>97733</v>
+        <v>92480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökhult Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575686</v>
+        <v>575695</v>
       </c>
       <c r="R11" t="n">
-        <v>6338891</v>
+        <v>6338740</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1691,12 +1719,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,33 +1733,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115434703</t>
+          <t>https://artportalen.se/Sighting/135819616</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115474054</v>
+        <v>114872798</v>
       </c>
       <c r="B12" t="n">
-        <v>97733</v>
+        <v>96708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1739,21 +1768,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1763,14 +1792,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575680</v>
+        <v>575684</v>
       </c>
       <c r="R12" t="n">
-        <v>6338885</v>
+        <v>6338822</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1797,22 +1826,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1828,27 +1847,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115474054</t>
+          <t>https://artportalen.se/Sighting/114872798</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114872706</v>
+        <v>134039376</v>
       </c>
       <c r="B13" t="n">
-        <v>97394</v>
+        <v>96783</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,38 +1875,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575651</v>
+        <v>575675</v>
       </c>
       <c r="R13" t="n">
-        <v>6338972</v>
+        <v>6338821</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1914,12 +1929,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,7 +1943,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1946,16 +1960,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114872706</t>
+          <t>https://artportalen.se/Sighting/134039376</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114872719</v>
+        <v>134039377</v>
       </c>
       <c r="B14" t="n">
-        <v>97394</v>
+        <v>96783</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1963,38 +1977,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575678</v>
+        <v>575819</v>
       </c>
       <c r="R14" t="n">
-        <v>6338931</v>
+        <v>6338837</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2021,12 +2031,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2035,7 +2045,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2053,16 +2062,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114872719</t>
+          <t>https://artportalen.se/Sighting/134039377</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114872727</v>
+        <v>134039378</v>
       </c>
       <c r="B15" t="n">
-        <v>97394</v>
+        <v>96783</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,38 +2079,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575686</v>
+        <v>575798</v>
       </c>
       <c r="R15" t="n">
-        <v>6338891</v>
+        <v>6338862</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2128,12 +2133,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2142,7 +2147,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2160,16 +2164,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114872727</t>
+          <t>https://artportalen.se/Sighting/134039378</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114872769</v>
+        <v>134039379</v>
       </c>
       <c r="B16" t="n">
-        <v>97394</v>
+        <v>96783</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2177,38 +2181,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575684</v>
+        <v>575755</v>
       </c>
       <c r="R16" t="n">
-        <v>6338893</v>
+        <v>6338857</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2235,12 +2235,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2249,7 +2249,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2267,16 +2266,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114872769</t>
+          <t>https://artportalen.se/Sighting/134039379</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114872789</v>
+        <v>134039380</v>
       </c>
       <c r="B17" t="n">
-        <v>97394</v>
+        <v>96783</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2284,38 +2283,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575667</v>
+        <v>575719</v>
       </c>
       <c r="R17" t="n">
-        <v>6338849</v>
+        <v>6338853</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2342,12 +2337,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2356,7 +2351,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2374,16 +2368,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114872789</t>
+          <t>https://artportalen.se/Sighting/134039380</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115173183</v>
+        <v>115434703</v>
       </c>
       <c r="B18" t="n">
-        <v>97394</v>
+        <v>97733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2391,38 +2385,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2590</v>
+        <v>2569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575688</v>
+        <v>575686</v>
       </c>
       <c r="R18" t="n">
-        <v>6338871</v>
+        <v>6338891</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2449,22 +2439,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2473,34 +2453,33 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115173183</t>
+          <t>https://artportalen.se/Sighting/115434703</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115173284</v>
+        <v>115474054</v>
       </c>
       <c r="B19" t="n">
-        <v>97394</v>
+        <v>97733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2508,21 +2487,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2590</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2539,7 +2518,7 @@
         <v>575680</v>
       </c>
       <c r="R19" t="n">
-        <v>6338897</v>
+        <v>6338885</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2566,22 +2545,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,13 +2587,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115173284</t>
+          <t>https://artportalen.se/Sighting/115474054</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115173297</v>
+        <v>114872706</v>
       </c>
       <c r="B20" t="n">
         <v>97394</v>
@@ -2649,14 +2628,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
         <v>575651</v>
       </c>
       <c r="R20" t="n">
-        <v>6338902</v>
+        <v>6338972</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2683,22 +2662,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2714,27 +2683,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115173297</t>
+          <t>https://artportalen.se/Sighting/114872706</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134039371</v>
+        <v>114872719</v>
       </c>
       <c r="B21" t="n">
-        <v>97471</v>
+        <v>97394</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2760,16 +2729,20 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575685</v>
+        <v>575678</v>
       </c>
       <c r="R21" t="n">
-        <v>6338794</v>
+        <v>6338931</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2796,12 +2769,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,6 +2783,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2827,16 +2801,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039371</t>
+          <t>https://artportalen.se/Sighting/114872719</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134039372</v>
+        <v>114872727</v>
       </c>
       <c r="B22" t="n">
-        <v>97471</v>
+        <v>97394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,16 +2836,20 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575722</v>
+        <v>575686</v>
       </c>
       <c r="R22" t="n">
-        <v>6338748</v>
+        <v>6338891</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2898,12 +2876,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,6 +2890,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2929,16 +2908,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039372</t>
+          <t>https://artportalen.se/Sighting/114872727</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>114872751</v>
+        <v>114872769</v>
       </c>
       <c r="B23" t="n">
-        <v>96348</v>
+        <v>97394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2946,21 +2925,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2974,10 +2953,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575659</v>
+        <v>575684</v>
       </c>
       <c r="R23" t="n">
-        <v>6338885</v>
+        <v>6338893</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3036,16 +3015,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114872751</t>
+          <t>https://artportalen.se/Sighting/114872769</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123973813</v>
+        <v>114872789</v>
       </c>
       <c r="B24" t="n">
-        <v>92333</v>
+        <v>97394</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3053,37 +3032,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4217</v>
+        <v>2590</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gökklint, Gökklint, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575666</v>
+        <v>575667</v>
       </c>
       <c r="R24" t="n">
-        <v>6338964</v>
+        <v>6338849</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3107,12 +3090,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,6 +3104,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3138,16 +3122,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123973813</t>
+          <t>https://artportalen.se/Sighting/114872789</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134039364</v>
+        <v>115173183</v>
       </c>
       <c r="B25" t="n">
-        <v>91937</v>
+        <v>97394</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3155,34 +3139,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>2590</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575748</v>
+        <v>575688</v>
       </c>
       <c r="R25" t="n">
-        <v>6338783</v>
+        <v>6338871</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3209,12 +3197,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,33 +3221,34 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039364</t>
+          <t>https://artportalen.se/Sighting/115173183</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123973504</v>
+        <v>115173284</v>
       </c>
       <c r="B26" t="n">
-        <v>57950</v>
+        <v>97394</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3257,39 +3256,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hultemossen, Hultemossen, Sm</t>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575611</v>
+        <v>575680</v>
       </c>
       <c r="R26" t="n">
-        <v>6338932</v>
+        <v>6338897</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3316,12 +3314,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,33 +3338,34 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123973504</t>
+          <t>https://artportalen.se/Sighting/115173284</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134039368</v>
+        <v>115173297</v>
       </c>
       <c r="B27" t="n">
-        <v>57972</v>
+        <v>97394</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,34 +3373,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575711</v>
+        <v>575651</v>
       </c>
       <c r="R27" t="n">
-        <v>6338746</v>
+        <v>6338902</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3418,17 +3431,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Födosöksspår</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3437,33 +3455,34 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039368</t>
+          <t>https://artportalen.se/Sighting/115173297</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134039374</v>
+        <v>134039371</v>
       </c>
       <c r="B28" t="n">
-        <v>5181</v>
+        <v>97471</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3471,21 +3490,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3495,7 +3514,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575729</v>
+        <v>575685</v>
       </c>
       <c r="R28" t="n">
         <v>6338794</v>
@@ -3533,11 +3552,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3561,16 +3575,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039374</t>
+          <t>https://artportalen.se/Sighting/134039371</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115173209</v>
+        <v>134039372</v>
       </c>
       <c r="B29" t="n">
-        <v>58327</v>
+        <v>97471</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3578,46 +3592,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>2590</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575688</v>
+        <v>575722</v>
       </c>
       <c r="R29" t="n">
-        <v>6338871</v>
+        <v>6338748</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3644,22 +3646,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,77 +3666,69 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115173209</t>
+          <t>https://artportalen.se/Sighting/134039372</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115173318</v>
+        <v>135819316</v>
       </c>
       <c r="B30" t="n">
-        <v>58114</v>
+        <v>97547</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>2590</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökhult Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575598</v>
+        <v>575669</v>
       </c>
       <c r="R30" t="n">
-        <v>6338927</v>
+        <v>6338811</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3768,22 +3752,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3792,83 +3766,76 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115173318</t>
+          <t>https://artportalen.se/Sighting/135819316</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115473966</v>
+        <v>135819339</v>
       </c>
       <c r="B31" t="n">
-        <v>58114</v>
+        <v>97547</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>2590</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökhult Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575648</v>
+        <v>575669</v>
       </c>
       <c r="R31" t="n">
-        <v>6338867</v>
+        <v>6338882</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3892,22 +3859,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3916,33 +3873,34 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115473966</t>
+          <t>https://artportalen.se/Sighting/135819339</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134039363</v>
+        <v>135819391</v>
       </c>
       <c r="B32" t="n">
-        <v>5201</v>
+        <v>97547</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,37 +3908,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökhult Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575729</v>
+        <v>575690</v>
       </c>
       <c r="R32" t="n">
-        <v>6338794</v>
+        <v>6338855</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4004,17 +3966,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4023,33 +3980,34 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039363</t>
+          <t>https://artportalen.se/Sighting/135819391</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115473932</v>
+        <v>135819423</v>
       </c>
       <c r="B33" t="n">
-        <v>97983</v>
+        <v>97547</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,21 +4015,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>2590</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4081,17 +4039,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökhult Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575648</v>
+        <v>575647</v>
       </c>
       <c r="R33" t="n">
-        <v>6338867</v>
+        <v>6338758</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4115,22 +4073,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,18 +4094,1780 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135819423</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135819464</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97547</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gökhult Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>575644</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6338893</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135819464</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135819508</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97547</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gökhult Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>575666</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6338786</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135819508</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>114872751</v>
+      </c>
+      <c r="B36" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>575659</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6338885</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114872751</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135819503</v>
+      </c>
+      <c r="B37" t="n">
+        <v>96609</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gökhult Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>575666</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6338786</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135819503</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>123973813</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92333</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gökklint, Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>575666</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6338964</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123973813</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134039364</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>575748</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6338783</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039364</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135819296</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gökhult Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>575749</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6338671</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135819296</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123973504</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hultemossen, Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>575611</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6338932</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123973504</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134039368</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>575711</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6338746</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Födosöksspår</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039368</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134039374</v>
+      </c>
+      <c r="B43" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>575729</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6338794</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039374</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>115173209</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>575688</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6338871</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115173209</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>115173318</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>575598</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6338927</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115173318</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>115473966</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>575648</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6338867</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115473966</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134039363</v>
+      </c>
+      <c r="B47" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>575729</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6338794</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039363</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>115473932</v>
+      </c>
+      <c r="B48" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>575648</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6338867</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/115473932</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135819395</v>
+      </c>
+      <c r="B49" t="n">
+        <v>100039</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222364</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Skärmstarr</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carex remota</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gökhult Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>575690</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6338855</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135819395</t>
         </is>
       </c>
     </row>
@@ -4195,6 +5905,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135819428</v>
       </c>
       <c r="B3" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135819786</v>
       </c>
       <c r="B4" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135819791</v>
       </c>
       <c r="B5" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135819811</v>
       </c>
       <c r="B6" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135819813</v>
       </c>
       <c r="B7" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135819199</v>
       </c>
       <c r="B8" t="n">
-        <v>96705</v>
+        <v>96707</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135819616</v>
       </c>
       <c r="B11" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>135819316</v>
       </c>
       <c r="B30" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>135819339</v>
       </c>
       <c r="B31" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>135819391</v>
       </c>
       <c r="B32" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>135819423</v>
       </c>
       <c r="B33" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>135819464</v>
       </c>
       <c r="B34" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>135819508</v>
       </c>
       <c r="B35" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>135819503</v>
       </c>
       <c r="B37" t="n">
-        <v>96609</v>
+        <v>96611</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>135819395</v>
       </c>
       <c r="B49" t="n">
-        <v>100039</v>
+        <v>100041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1727,6 +1727,11 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Jämför bilderna med en annan helt säkert bestämd rynkskinn från en annan lokal: https://artportalen.se/Sighting/135954717</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135819428</v>
       </c>
       <c r="B3" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135819786</v>
       </c>
       <c r="B4" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135819791</v>
       </c>
       <c r="B5" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135819811</v>
       </c>
       <c r="B6" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135819813</v>
       </c>
       <c r="B7" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135819199</v>
       </c>
       <c r="B8" t="n">
-        <v>96707</v>
+        <v>96724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135819616</v>
       </c>
       <c r="B11" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>135819316</v>
       </c>
       <c r="B30" t="n">
-        <v>97549</v>
+        <v>97566</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>135819339</v>
       </c>
       <c r="B31" t="n">
-        <v>97549</v>
+        <v>97566</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>135819391</v>
       </c>
       <c r="B32" t="n">
-        <v>97549</v>
+        <v>97566</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>135819423</v>
       </c>
       <c r="B33" t="n">
-        <v>97549</v>
+        <v>97566</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>135819464</v>
       </c>
       <c r="B34" t="n">
-        <v>97549</v>
+        <v>97566</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>135819508</v>
       </c>
       <c r="B35" t="n">
-        <v>97549</v>
+        <v>97566</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135819503</v>
       </c>
       <c r="B37" t="n">
-        <v>96611</v>
+        <v>96628</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>135819296</v>
       </c>
       <c r="B40" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>135819395</v>
       </c>
       <c r="B49" t="n">
-        <v>100041</v>
+        <v>100058</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135819428</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135819786</v>
       </c>
       <c r="B4" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135819791</v>
       </c>
       <c r="B5" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135819811</v>
       </c>
       <c r="B6" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135819813</v>
       </c>
       <c r="B7" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135819199</v>
       </c>
       <c r="B8" t="n">
-        <v>96724</v>
+        <v>96725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135819616</v>
       </c>
       <c r="B11" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>135819316</v>
       </c>
       <c r="B30" t="n">
-        <v>97566</v>
+        <v>97567</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>135819339</v>
       </c>
       <c r="B31" t="n">
-        <v>97566</v>
+        <v>97567</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>135819391</v>
       </c>
       <c r="B32" t="n">
-        <v>97566</v>
+        <v>97567</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>135819423</v>
       </c>
       <c r="B33" t="n">
-        <v>97566</v>
+        <v>97567</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>135819464</v>
       </c>
       <c r="B34" t="n">
-        <v>97566</v>
+        <v>97567</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>135819508</v>
       </c>
       <c r="B35" t="n">
-        <v>97566</v>
+        <v>97567</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135819503</v>
       </c>
       <c r="B37" t="n">
-        <v>96628</v>
+        <v>96629</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>135819296</v>
       </c>
       <c r="B40" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>135819395</v>
       </c>
       <c r="B49" t="n">
-        <v>100058</v>
+        <v>100060</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135819428</v>
       </c>
       <c r="B3" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135819786</v>
       </c>
       <c r="B4" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135819791</v>
       </c>
       <c r="B5" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135819811</v>
       </c>
       <c r="B6" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135819813</v>
       </c>
       <c r="B7" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135819199</v>
       </c>
       <c r="B8" t="n">
-        <v>96725</v>
+        <v>96726</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135819616</v>
       </c>
       <c r="B11" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>135819316</v>
       </c>
       <c r="B30" t="n">
-        <v>97567</v>
+        <v>97568</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>135819339</v>
       </c>
       <c r="B31" t="n">
-        <v>97567</v>
+        <v>97568</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>135819391</v>
       </c>
       <c r="B32" t="n">
-        <v>97567</v>
+        <v>97568</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>135819423</v>
       </c>
       <c r="B33" t="n">
-        <v>97567</v>
+        <v>97568</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>135819464</v>
       </c>
       <c r="B34" t="n">
-        <v>97567</v>
+        <v>97568</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>135819508</v>
       </c>
       <c r="B35" t="n">
-        <v>97567</v>
+        <v>97568</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135819503</v>
       </c>
       <c r="B37" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>135819395</v>
       </c>
       <c r="B49" t="n">
-        <v>100060</v>
+        <v>100061</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135819428</v>
       </c>
       <c r="B3" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135819786</v>
       </c>
       <c r="B4" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135819791</v>
       </c>
       <c r="B5" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135819811</v>
       </c>
       <c r="B6" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135819813</v>
       </c>
       <c r="B7" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135819199</v>
       </c>
       <c r="B8" t="n">
-        <v>96726</v>
+        <v>96727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135819616</v>
       </c>
       <c r="B11" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>135819316</v>
       </c>
       <c r="B30" t="n">
-        <v>97568</v>
+        <v>97569</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>135819339</v>
       </c>
       <c r="B31" t="n">
-        <v>97568</v>
+        <v>97569</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>135819391</v>
       </c>
       <c r="B32" t="n">
-        <v>97568</v>
+        <v>97569</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>135819423</v>
       </c>
       <c r="B33" t="n">
-        <v>97568</v>
+        <v>97569</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>135819464</v>
       </c>
       <c r="B34" t="n">
-        <v>97568</v>
+        <v>97569</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>135819508</v>
       </c>
       <c r="B35" t="n">
-        <v>97568</v>
+        <v>97569</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135819503</v>
       </c>
       <c r="B37" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>135819296</v>
       </c>
       <c r="B40" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>135819395</v>
       </c>
       <c r="B49" t="n">
-        <v>100061</v>
+        <v>100062</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135819428</v>
       </c>
       <c r="B3" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135819786</v>
       </c>
       <c r="B4" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135819791</v>
       </c>
       <c r="B5" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135819811</v>
       </c>
       <c r="B6" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135819813</v>
       </c>
       <c r="B7" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135819199</v>
       </c>
       <c r="B8" t="n">
-        <v>96727</v>
+        <v>96733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135819616</v>
       </c>
       <c r="B11" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>135819316</v>
       </c>
       <c r="B30" t="n">
-        <v>97569</v>
+        <v>97575</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>135819339</v>
       </c>
       <c r="B31" t="n">
-        <v>97569</v>
+        <v>97575</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>135819391</v>
       </c>
       <c r="B32" t="n">
-        <v>97569</v>
+        <v>97575</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>135819423</v>
       </c>
       <c r="B33" t="n">
-        <v>97569</v>
+        <v>97575</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>135819464</v>
       </c>
       <c r="B34" t="n">
-        <v>97569</v>
+        <v>97575</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>135819508</v>
       </c>
       <c r="B35" t="n">
-        <v>97569</v>
+        <v>97575</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135819503</v>
       </c>
       <c r="B37" t="n">
-        <v>96631</v>
+        <v>96637</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>135819296</v>
       </c>
       <c r="B40" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>135819395</v>
       </c>
       <c r="B49" t="n">
-        <v>100062</v>
+        <v>100068</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135819428</v>
       </c>
       <c r="B3" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135819786</v>
       </c>
       <c r="B4" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135819791</v>
       </c>
       <c r="B5" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135819811</v>
       </c>
       <c r="B6" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135819813</v>
       </c>
       <c r="B7" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135819199</v>
       </c>
       <c r="B8" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135819616</v>
       </c>
       <c r="B11" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>135819316</v>
       </c>
       <c r="B30" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>135819339</v>
       </c>
       <c r="B31" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>135819391</v>
       </c>
       <c r="B32" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>135819423</v>
       </c>
       <c r="B33" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>135819464</v>
       </c>
       <c r="B34" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>135819508</v>
       </c>
       <c r="B35" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135819503</v>
       </c>
       <c r="B37" t="n">
-        <v>96637</v>
+        <v>96638</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>135819296</v>
       </c>
       <c r="B40" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>135819395</v>
       </c>
       <c r="B49" t="n">
-        <v>100068</v>
+        <v>100069</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135819428</v>
       </c>
       <c r="B3" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135819786</v>
       </c>
       <c r="B4" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135819791</v>
       </c>
       <c r="B5" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135819811</v>
       </c>
       <c r="B6" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135819813</v>
       </c>
       <c r="B7" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135819199</v>
       </c>
       <c r="B8" t="n">
-        <v>96734</v>
+        <v>96745</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135819616</v>
       </c>
       <c r="B11" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>135819316</v>
       </c>
       <c r="B30" t="n">
-        <v>97576</v>
+        <v>97587</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>135819339</v>
       </c>
       <c r="B31" t="n">
-        <v>97576</v>
+        <v>97587</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>135819391</v>
       </c>
       <c r="B32" t="n">
-        <v>97576</v>
+        <v>97587</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>135819423</v>
       </c>
       <c r="B33" t="n">
-        <v>97576</v>
+        <v>97587</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>135819464</v>
       </c>
       <c r="B34" t="n">
-        <v>97576</v>
+        <v>97587</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>135819508</v>
       </c>
       <c r="B35" t="n">
-        <v>97576</v>
+        <v>97587</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135819503</v>
       </c>
       <c r="B37" t="n">
-        <v>96638</v>
+        <v>96649</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>135819296</v>
       </c>
       <c r="B40" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>135819395</v>
       </c>
       <c r="B49" t="n">
-        <v>100069</v>
+        <v>100080</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135819428</v>
       </c>
       <c r="B3" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135819786</v>
       </c>
       <c r="B4" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135819791</v>
       </c>
       <c r="B5" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135819811</v>
       </c>
       <c r="B6" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135819813</v>
       </c>
       <c r="B7" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135819199</v>
       </c>
       <c r="B8" t="n">
-        <v>96745</v>
+        <v>96758</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135819616</v>
       </c>
       <c r="B11" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>135819316</v>
       </c>
       <c r="B30" t="n">
-        <v>97587</v>
+        <v>97600</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>135819339</v>
       </c>
       <c r="B31" t="n">
-        <v>97587</v>
+        <v>97600</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>135819391</v>
       </c>
       <c r="B32" t="n">
-        <v>97587</v>
+        <v>97600</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>135819423</v>
       </c>
       <c r="B33" t="n">
-        <v>97587</v>
+        <v>97600</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>135819464</v>
       </c>
       <c r="B34" t="n">
-        <v>97587</v>
+        <v>97600</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>135819508</v>
       </c>
       <c r="B35" t="n">
-        <v>97587</v>
+        <v>97600</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135819503</v>
       </c>
       <c r="B37" t="n">
-        <v>96649</v>
+        <v>96662</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>135819296</v>
       </c>
       <c r="B40" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>135819395</v>
       </c>
       <c r="B49" t="n">
-        <v>100080</v>
+        <v>100093</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135819428</v>
       </c>
       <c r="B3" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135819786</v>
       </c>
       <c r="B4" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135819791</v>
       </c>
       <c r="B5" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135819811</v>
       </c>
       <c r="B6" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135819813</v>
       </c>
       <c r="B7" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135819199</v>
       </c>
       <c r="B8" t="n">
-        <v>96758</v>
+        <v>96759</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135819616</v>
       </c>
       <c r="B11" t="n">
-        <v>92519</v>
+        <v>92520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>135819316</v>
       </c>
       <c r="B30" t="n">
-        <v>97600</v>
+        <v>97601</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>135819339</v>
       </c>
       <c r="B31" t="n">
-        <v>97600</v>
+        <v>97601</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>135819391</v>
       </c>
       <c r="B32" t="n">
-        <v>97600</v>
+        <v>97601</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>135819423</v>
       </c>
       <c r="B33" t="n">
-        <v>97600</v>
+        <v>97601</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>135819464</v>
       </c>
       <c r="B34" t="n">
-        <v>97600</v>
+        <v>97601</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>135819508</v>
       </c>
       <c r="B35" t="n">
-        <v>97600</v>
+        <v>97601</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135819503</v>
       </c>
       <c r="B37" t="n">
-        <v>96662</v>
+        <v>96663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>135819395</v>
       </c>
       <c r="B49" t="n">
-        <v>100093</v>
+        <v>100094</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135819428</v>
       </c>
       <c r="B3" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135819786</v>
       </c>
       <c r="B4" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135819791</v>
       </c>
       <c r="B5" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135819811</v>
       </c>
       <c r="B6" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135819813</v>
       </c>
       <c r="B7" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135819199</v>
       </c>
       <c r="B8" t="n">
-        <v>96759</v>
+        <v>96772</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135819616</v>
       </c>
       <c r="B11" t="n">
-        <v>92520</v>
+        <v>92533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>135819316</v>
       </c>
       <c r="B30" t="n">
-        <v>97601</v>
+        <v>97614</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>135819339</v>
       </c>
       <c r="B31" t="n">
-        <v>97601</v>
+        <v>97614</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>135819391</v>
       </c>
       <c r="B32" t="n">
-        <v>97601</v>
+        <v>97614</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>135819423</v>
       </c>
       <c r="B33" t="n">
-        <v>97601</v>
+        <v>97614</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>135819464</v>
       </c>
       <c r="B34" t="n">
-        <v>97601</v>
+        <v>97614</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>135819508</v>
       </c>
       <c r="B35" t="n">
-        <v>97601</v>
+        <v>97614</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>135819503</v>
       </c>
       <c r="B37" t="n">
-        <v>96663</v>
+        <v>96676</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>135819296</v>
       </c>
       <c r="B40" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>135819395</v>
       </c>
       <c r="B49" t="n">
-        <v>100094</v>
+        <v>100107</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1654,7 +1654,7 @@
         <v>135819616</v>
       </c>
       <c r="B11" t="n">
-        <v>92533</v>
+        <v>92534</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
